--- a/artfynd/A 4375-2022 artfynd.xlsx
+++ b/artfynd/A 4375-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4375-2022 artfynd.xlsx
+++ b/artfynd/A 4375-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4424,10 +4424,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111311816</v>
+        <v>111308434</v>
       </c>
       <c r="B35" t="n">
-        <v>91005</v>
+        <v>78578</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4436,41 +4436,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590679</v>
+        <v>590592.3607059828</v>
       </c>
       <c r="R35" t="n">
-        <v>7040619</v>
+        <v>7040261.380789872</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4500,18 +4498,27 @@
           <t>2023-08-06</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-08-06</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4530,10 +4537,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111308434</v>
+        <v>111308527</v>
       </c>
       <c r="B36" t="n">
-        <v>78578</v>
+        <v>89686</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4546,21 +4553,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4571,13 +4578,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590592.3607059828</v>
+        <v>590571.6374187953</v>
       </c>
       <c r="R36" t="n">
-        <v>7040261.380789872</v>
+        <v>7040376.160066846</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4606,7 +4613,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4616,7 +4623,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,22 +4638,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111308527</v>
+        <v>111305012</v>
       </c>
       <c r="B37" t="n">
-        <v>89686</v>
+        <v>89845</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4655,25 +4662,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4684,13 +4691,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590571.6374187953</v>
+        <v>590677.6718517016</v>
       </c>
       <c r="R37" t="n">
-        <v>7040376.160066846</v>
+        <v>7040615.262823105</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4719,7 +4726,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4736,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4744,22 +4751,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111305012</v>
+        <v>111305042</v>
       </c>
       <c r="B38" t="n">
-        <v>89845</v>
+        <v>89405</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4768,25 +4775,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4797,10 +4804,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590677.6718517016</v>
+        <v>590677.0058343092</v>
       </c>
       <c r="R38" t="n">
-        <v>7040615.262823105</v>
+        <v>7040607.195673673</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4869,10 +4876,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111305042</v>
+        <v>111307637</v>
       </c>
       <c r="B39" t="n">
-        <v>89405</v>
+        <v>94134</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4885,21 +4892,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4910,10 +4917,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590677.0058343092</v>
+        <v>590658.1836587854</v>
       </c>
       <c r="R39" t="n">
-        <v>7040607.195673673</v>
+        <v>7040277.113733714</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4982,10 +4989,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111307637</v>
+        <v>111320026</v>
       </c>
       <c r="B40" t="n">
-        <v>94134</v>
+        <v>89686</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4998,38 +5005,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valforsen, Ång</t>
+          <t>Loka, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590658.1836587854</v>
+        <v>590728.1019840735</v>
       </c>
       <c r="R40" t="n">
-        <v>7040277.113733714</v>
+        <v>7040573.773426552</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5083,19 +5089,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111320026</v>
+        <v>111320027</v>
       </c>
       <c r="B41" t="n">
         <v>89686</v>
@@ -5135,10 +5141,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590728.1019840735</v>
+        <v>590668.9787260931</v>
       </c>
       <c r="R41" t="n">
-        <v>7040573.773426552</v>
+        <v>7040606.073147954</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5207,10 +5213,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111320027</v>
+        <v>111307853</v>
       </c>
       <c r="B42" t="n">
-        <v>89686</v>
+        <v>89405</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5223,37 +5229,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Loka, Ång</t>
+          <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590668.9787260931</v>
+        <v>590640.5765326766</v>
       </c>
       <c r="R42" t="n">
-        <v>7040606.073147954</v>
+        <v>7040250.677298564</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5307,22 +5314,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111307853</v>
+        <v>111311113</v>
       </c>
       <c r="B43" t="n">
-        <v>89405</v>
+        <v>89369</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5331,25 +5338,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5360,13 +5367,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>590640.5765326766</v>
+        <v>590571.6374187953</v>
       </c>
       <c r="R43" t="n">
-        <v>7040250.677298564</v>
+        <v>7040376.160066846</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5420,22 +5427,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111311113</v>
+        <v>111308121</v>
       </c>
       <c r="B44" t="n">
-        <v>89369</v>
+        <v>90187</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5444,25 +5451,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>2014</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5473,13 +5480,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>590571.6374187953</v>
+        <v>590607.2776005382</v>
       </c>
       <c r="R44" t="n">
-        <v>7040376.160066846</v>
+        <v>7040256.438550681</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5519,6 +5526,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5533,22 +5545,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111308121</v>
+        <v>111305036</v>
       </c>
       <c r="B45" t="n">
-        <v>90187</v>
+        <v>89845</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,25 +5569,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2014</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5586,10 +5598,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590607.2776005382</v>
+        <v>590677.0058343092</v>
       </c>
       <c r="R45" t="n">
-        <v>7040256.438550681</v>
+        <v>7040607.195673673</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5632,11 +5644,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5663,7 +5670,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111305036</v>
+        <v>111305206</v>
       </c>
       <c r="B46" t="n">
         <v>89845</v>
@@ -5704,10 +5711,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>590677.0058343092</v>
+        <v>590706.3868867881</v>
       </c>
       <c r="R46" t="n">
-        <v>7040607.195673673</v>
+        <v>7040581.651012956</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5776,10 +5783,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111305206</v>
+        <v>111311509</v>
       </c>
       <c r="B47" t="n">
-        <v>89845</v>
+        <v>79642</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,39 +5795,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590706.3868867881</v>
+        <v>590707</v>
       </c>
       <c r="R47" t="n">
-        <v>7040581.651012956</v>
+        <v>7040485</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5850,27 +5859,18 @@
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111311509</v>
+        <v>111308600</v>
       </c>
       <c r="B48" t="n">
-        <v>79642</v>
+        <v>78578</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5901,44 +5901,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>590707</v>
+        <v>590571.6374187953</v>
       </c>
       <c r="R48" t="n">
-        <v>7040485</v>
+        <v>7040376.160066846</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5965,40 +5963,49 @@
           <t>2023-08-06</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-08-06</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111308600</v>
+        <v>111311401</v>
       </c>
       <c r="B49" t="n">
-        <v>78578</v>
+        <v>89686</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6011,21 +6018,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6036,13 +6043,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590571.6374187953</v>
+        <v>590706.4606926481</v>
       </c>
       <c r="R49" t="n">
-        <v>7040376.160066846</v>
+        <v>7040484.625072884</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6071,7 +6078,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6088,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,22 +6103,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111311401</v>
+        <v>111309827</v>
       </c>
       <c r="B50" t="n">
-        <v>89686</v>
+        <v>77515</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6124,21 +6131,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6149,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590706.4606926481</v>
+        <v>590614.0068928505</v>
       </c>
       <c r="R50" t="n">
-        <v>7040484.625072884</v>
+        <v>7040350.534422184</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6184,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6194,7 +6201,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6221,10 +6228,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111309827</v>
+        <v>111305920</v>
       </c>
       <c r="B51" t="n">
-        <v>77515</v>
+        <v>89425</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6237,21 +6244,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6262,10 +6269,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>590614.0068928505</v>
+        <v>590734.7799036079</v>
       </c>
       <c r="R51" t="n">
-        <v>7040350.534422184</v>
+        <v>7040527.908902652</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6297,7 +6304,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6307,7 +6314,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,10 +6341,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111305920</v>
+        <v>111308194</v>
       </c>
       <c r="B52" t="n">
-        <v>89425</v>
+        <v>78612</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6346,25 +6353,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6375,10 +6382,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590734.7799036079</v>
+        <v>590607.2776005382</v>
       </c>
       <c r="R52" t="n">
-        <v>7040527.908902652</v>
+        <v>7040256.438550681</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6447,10 +6454,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111308194</v>
+        <v>111311410</v>
       </c>
       <c r="B53" t="n">
-        <v>78612</v>
+        <v>56543</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6459,39 +6466,44 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590607.2776005382</v>
+        <v>590706.4606926481</v>
       </c>
       <c r="R53" t="n">
-        <v>7040256.438550681</v>
+        <v>7040484.625072884</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6560,10 +6572,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111311410</v>
+        <v>111311029</v>
       </c>
       <c r="B54" t="n">
-        <v>56543</v>
+        <v>89590</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6572,44 +6584,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590706.4606926481</v>
+        <v>590702.9273836177</v>
       </c>
       <c r="R54" t="n">
-        <v>7040484.625072884</v>
+        <v>7040451.435986779</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6678,10 +6685,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111311029</v>
+        <v>111320024</v>
       </c>
       <c r="B55" t="n">
-        <v>89590</v>
+        <v>89405</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6690,42 +6697,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Valforsen, Ång</t>
+          <t>Loka, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590702.9273836177</v>
+        <v>590670.6438133246</v>
       </c>
       <c r="R55" t="n">
-        <v>7040451.435986779</v>
+        <v>7040626.240984956</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6779,22 +6785,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111320024</v>
+        <v>111305463</v>
       </c>
       <c r="B56" t="n">
-        <v>89405</v>
+        <v>89686</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6807,37 +6813,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Loka, Ång</t>
+          <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590670.6438133246</v>
+        <v>590730.310987493</v>
       </c>
       <c r="R56" t="n">
-        <v>7040626.240984956</v>
+        <v>7040559.081015749</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6891,22 +6898,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111305463</v>
+        <v>111307902</v>
       </c>
       <c r="B57" t="n">
-        <v>89686</v>
+        <v>89405</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6919,21 +6926,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6944,10 +6951,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590730.310987493</v>
+        <v>590642.5312889211</v>
       </c>
       <c r="R57" t="n">
-        <v>7040559.081015749</v>
+        <v>7040244.919611955</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7016,10 +7023,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111307902</v>
+        <v>111311518</v>
       </c>
       <c r="B58" t="n">
-        <v>89405</v>
+        <v>90725</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7032,35 +7039,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>590642.5312889211</v>
+        <v>590715</v>
       </c>
       <c r="R58" t="n">
-        <v>7040244.919611955</v>
+        <v>7040485</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7087,22 +7096,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7111,6 +7110,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7129,10 +7129,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111311518</v>
+        <v>111310603</v>
       </c>
       <c r="B59" t="n">
-        <v>90725</v>
+        <v>89755</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7141,44 +7141,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>590715</v>
+        <v>590571.6374187953</v>
       </c>
       <c r="R59" t="n">
-        <v>7040485</v>
+        <v>7040376.160066846</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7202,12 +7200,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7216,29 +7224,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111310603</v>
+        <v>111312274</v>
       </c>
       <c r="B60" t="n">
-        <v>89755</v>
+        <v>90562</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7247,42 +7254,44 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>590571.6374187953</v>
+        <v>590719</v>
       </c>
       <c r="R60" t="n">
-        <v>7040376.160066846</v>
+        <v>7040613</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7309,49 +7318,40 @@
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>111312274</v>
+        <v>111308178</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>78578</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7364,37 +7364,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>590719</v>
+        <v>590604.1361025569</v>
       </c>
       <c r="R61" t="n">
-        <v>7040613</v>
+        <v>7040272.447424728</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7424,18 +7422,27 @@
           <t>2023-08-06</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-08-06</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7454,10 +7461,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>111308178</v>
+        <v>111310220</v>
       </c>
       <c r="B62" t="n">
-        <v>78578</v>
+        <v>77515</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7470,21 +7477,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7495,13 +7502,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>590604.1361025569</v>
+        <v>590571.6374187953</v>
       </c>
       <c r="R62" t="n">
-        <v>7040272.447424728</v>
+        <v>7040376.160066846</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7555,22 +7562,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>111310220</v>
+        <v>111308606</v>
       </c>
       <c r="B63" t="n">
-        <v>77515</v>
+        <v>78579</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7583,21 +7590,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7643,7 +7650,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7653,7 +7660,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7680,10 +7687,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>111308606</v>
+        <v>111311377</v>
       </c>
       <c r="B64" t="n">
-        <v>78579</v>
+        <v>90065</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7692,25 +7699,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>898</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7721,13 +7728,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>590571.6374187953</v>
+        <v>590706.4606926481</v>
       </c>
       <c r="R64" t="n">
-        <v>7040376.160066846</v>
+        <v>7040484.625072884</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7756,7 +7763,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7766,7 +7773,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7781,22 +7788,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>111311377</v>
+        <v>111304912</v>
       </c>
       <c r="B65" t="n">
-        <v>90065</v>
+        <v>89405</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7805,25 +7812,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7834,10 +7841,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>590706.4606926481</v>
+        <v>590678.899579621</v>
       </c>
       <c r="R65" t="n">
-        <v>7040484.625072884</v>
+        <v>7040619.321836494</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7906,10 +7913,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>111304912</v>
+        <v>111310851</v>
       </c>
       <c r="B66" t="n">
-        <v>89405</v>
+        <v>89558</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7918,25 +7925,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7947,13 +7954,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>590678.899579621</v>
+        <v>590571.6374187953</v>
       </c>
       <c r="R66" t="n">
-        <v>7040619.321836494</v>
+        <v>7040376.160066846</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8007,22 +8014,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>111310851</v>
+        <v>111870830</v>
       </c>
       <c r="B67" t="n">
-        <v>89558</v>
+        <v>90812</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8031,39 +8038,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1503</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Valforsen, Ång</t>
+          <t>Valforsen (Valforsen), Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>590571.6374187953</v>
+        <v>590558</v>
       </c>
       <c r="R67" t="n">
-        <v>7040376.160066846</v>
+        <v>7040400</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8090,22 +8097,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,10 +8129,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>111870830</v>
+        <v>111870990</v>
       </c>
       <c r="B68" t="n">
-        <v>90812</v>
+        <v>90800</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8148,21 +8145,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8173,10 +8170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>590558</v>
+        <v>590570</v>
       </c>
       <c r="R68" t="n">
-        <v>7040400</v>
+        <v>7040376</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8235,10 +8232,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>111870990</v>
+        <v>111881310</v>
       </c>
       <c r="B69" t="n">
-        <v>90800</v>
+        <v>89559</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8247,39 +8244,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Valforsen (Valforsen), Ång</t>
+          <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>590570</v>
+        <v>590739</v>
       </c>
       <c r="R69" t="n">
-        <v>7040376</v>
+        <v>7040524</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8338,10 +8334,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>111881310</v>
+        <v>111870127</v>
       </c>
       <c r="B70" t="n">
-        <v>89559</v>
+        <v>89539</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8354,34 +8350,35 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Valforsen, Ång</t>
+          <t>Valforsen (Valforsen), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>590739</v>
+        <v>590710</v>
       </c>
       <c r="R70" t="n">
-        <v>7040524</v>
+        <v>7040582</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8440,10 +8437,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>111870127</v>
+        <v>111881322</v>
       </c>
       <c r="B71" t="n">
-        <v>89539</v>
+        <v>56446</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8456,35 +8453,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Valforsen (Valforsen), Ång</t>
+          <t>Valforsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>590710</v>
+        <v>590615</v>
       </c>
       <c r="R71" t="n">
-        <v>7040582</v>
+        <v>7040279</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8543,10 +8544,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>111881322</v>
+        <v>111871585</v>
       </c>
       <c r="B72" t="n">
-        <v>56446</v>
+        <v>89539</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8559,39 +8560,35 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Valforsen, Ång</t>
+          <t>Valforsen (Valforsen), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>590615</v>
+        <v>590630</v>
       </c>
       <c r="R72" t="n">
-        <v>7040279</v>
+        <v>7040267</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8650,10 +8647,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>111871585</v>
+        <v>111870139</v>
       </c>
       <c r="B73" t="n">
-        <v>89539</v>
+        <v>89979</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8662,25 +8659,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8691,10 +8688,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>590630</v>
+        <v>590710</v>
       </c>
       <c r="R73" t="n">
-        <v>7040267</v>
+        <v>7040582</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8750,109 +8747,6 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>111870139</v>
-      </c>
-      <c r="B74" t="n">
-        <v>89979</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Valforsen (Valforsen), Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>590710</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7040582</v>
-      </c>
-      <c r="S74" t="n">
-        <v>20</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
